--- a/data/reference/KMate_University_Requirements_AppReady.xlsx
+++ b/data/reference/KMate_University_Requirements_AppReady.xlsx
@@ -17393,7 +17393,9 @@
       <x:c r="F7" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="str"/>
+      <x:c r="G7" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H7" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -17550,7 +17552,9 @@
       <x:c r="F10" s="14" t="str">
         <x:v>other</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="str"/>
+      <x:c r="G10" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H10" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -17654,7 +17658,9 @@
       <x:c r="F12" s="14" t="str">
         <x:v>university, rd</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="str"/>
+      <x:c r="G12" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H12" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -17703,9 +17709,11 @@
         <x:v>University Recommendation Track + Embassy; Global Network handled separately</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>embassy, global_network</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="str"/>
+        <x:v>embassy</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H13" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -17756,7 +17764,9 @@
       <x:c r="F14" s="14" t="str">
         <x:v>university, general</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="str"/>
+      <x:c r="G14" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H14" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -17807,7 +17817,9 @@
       <x:c r="F15" s="14" t="str">
         <x:v>embassy, rd, general</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="str"/>
+      <x:c r="G15" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H15" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -17858,7 +17870,9 @@
       <x:c r="F16" s="14" t="str">
         <x:v>embassy, university, general</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="str"/>
+      <x:c r="G16" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H16" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -17909,7 +17923,9 @@
       <x:c r="F17" s="14" t="str">
         <x:v>embassy, university, rd, general</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="str"/>
+      <x:c r="G17" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H17" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -17960,7 +17976,9 @@
       <x:c r="F18" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="str"/>
+      <x:c r="G18" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H18" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18011,7 +18029,9 @@
       <x:c r="F19" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="str"/>
+      <x:c r="G19" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H19" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18062,7 +18082,9 @@
       <x:c r="F20" s="14" t="str">
         <x:v>embassy, university, rd, general</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="str"/>
+      <x:c r="G20" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H20" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18113,7 +18135,9 @@
       <x:c r="F21" s="14" t="str">
         <x:v>other</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="str"/>
+      <x:c r="G21" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H21" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18164,7 +18188,9 @@
       <x:c r="F22" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="str"/>
+      <x:c r="G22" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H22" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18215,7 +18241,9 @@
       <x:c r="F23" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="str"/>
+      <x:c r="G23" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H23" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18266,7 +18294,9 @@
       <x:c r="F24" s="14" t="str">
         <x:v>other</x:v>
       </x:c>
-      <x:c r="G24" s="14" t="str"/>
+      <x:c r="G24" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H24" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18317,7 +18347,9 @@
       <x:c r="F25" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G25" s="14" t="str"/>
+      <x:c r="G25" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H25" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18368,7 +18400,9 @@
       <x:c r="F26" s="14" t="str">
         <x:v>other</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="str"/>
+      <x:c r="G26" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H26" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18419,7 +18453,9 @@
       <x:c r="F27" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="str"/>
+      <x:c r="G27" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H27" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18470,7 +18506,9 @@
       <x:c r="F28" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G28" s="14" t="str"/>
+      <x:c r="G28" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H28" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18521,7 +18559,9 @@
       <x:c r="F29" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G29" s="14" t="str"/>
+      <x:c r="G29" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H29" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18572,7 +18612,9 @@
       <x:c r="F30" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G30" s="14" t="str"/>
+      <x:c r="G30" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H30" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18623,7 +18665,9 @@
       <x:c r="F31" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G31" s="14" t="str"/>
+      <x:c r="G31" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H31" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18674,7 +18718,9 @@
       <x:c r="F32" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G32" s="14" t="str"/>
+      <x:c r="G32" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H32" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18725,7 +18771,9 @@
       <x:c r="F33" s="14" t="str">
         <x:v>embassy, university, research, general, r_gks</x:v>
       </x:c>
-      <x:c r="G33" s="14" t="str"/>
+      <x:c r="G33" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H33" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18776,7 +18824,9 @@
       <x:c r="F34" s="14" t="str">
         <x:v>university, general, r_gks</x:v>
       </x:c>
-      <x:c r="G34" s="14" t="str"/>
+      <x:c r="G34" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H34" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18827,7 +18877,9 @@
       <x:c r="F35" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G35" s="14" t="str"/>
+      <x:c r="G35" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H35" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18878,7 +18930,9 @@
       <x:c r="F36" s="14" t="str">
         <x:v>university, rd, general, r_gks</x:v>
       </x:c>
-      <x:c r="G36" s="14" t="str"/>
+      <x:c r="G36" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H36" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18929,7 +18983,9 @@
       <x:c r="F37" s="14" t="str">
         <x:v>university, rd, research, general, r_gks</x:v>
       </x:c>
-      <x:c r="G37" s="14" t="str"/>
+      <x:c r="G37" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H37" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -18980,7 +19036,9 @@
       <x:c r="F38" s="14" t="str">
         <x:v>university, rd, general</x:v>
       </x:c>
-      <x:c r="G38" s="14" t="str"/>
+      <x:c r="G38" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H38" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19031,7 +19089,9 @@
       <x:c r="F39" s="14" t="str">
         <x:v>university, research, general</x:v>
       </x:c>
-      <x:c r="G39" s="14" t="str"/>
+      <x:c r="G39" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H39" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19082,7 +19142,9 @@
       <x:c r="F40" s="14" t="str">
         <x:v>embassy, university, rd</x:v>
       </x:c>
-      <x:c r="G40" s="14" t="str"/>
+      <x:c r="G40" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H40" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19133,7 +19195,9 @@
       <x:c r="F41" s="14" t="str">
         <x:v>embassy, university, r_gks</x:v>
       </x:c>
-      <x:c r="G41" s="14" t="str"/>
+      <x:c r="G41" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H41" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19184,7 +19248,9 @@
       <x:c r="F42" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G42" s="14" t="str"/>
+      <x:c r="G42" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H42" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19235,7 +19301,9 @@
       <x:c r="F43" s="14" t="str">
         <x:v>university, rd, general</x:v>
       </x:c>
-      <x:c r="G43" s="14" t="str"/>
+      <x:c r="G43" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H43" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19286,7 +19354,9 @@
       <x:c r="F44" s="14" t="str">
         <x:v>university, rd</x:v>
       </x:c>
-      <x:c r="G44" s="14" t="str"/>
+      <x:c r="G44" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H44" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19390,7 +19460,9 @@
       <x:c r="F46" s="14" t="str">
         <x:v>embassy, university, global_network, general</x:v>
       </x:c>
-      <x:c r="G46" s="14" t="str"/>
+      <x:c r="G46" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H46" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19441,7 +19513,9 @@
       <x:c r="F47" s="14" t="str">
         <x:v>other</x:v>
       </x:c>
-      <x:c r="G47" s="14" t="str"/>
+      <x:c r="G47" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H47" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19492,7 +19566,9 @@
       <x:c r="F48" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G48" s="14" t="str"/>
+      <x:c r="G48" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H48" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19543,7 +19619,9 @@
       <x:c r="F49" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G49" s="14" t="str"/>
+      <x:c r="G49" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H49" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19594,7 +19672,9 @@
       <x:c r="F50" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G50" s="14" t="str"/>
+      <x:c r="G50" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H50" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19645,7 +19725,9 @@
       <x:c r="F51" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G51" s="14" t="str"/>
+      <x:c r="G51" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H51" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19696,7 +19778,9 @@
       <x:c r="F52" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G52" s="14" t="str"/>
+      <x:c r="G52" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H52" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19747,7 +19831,9 @@
       <x:c r="F53" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G53" s="14" t="str"/>
+      <x:c r="G53" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H53" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19798,7 +19884,9 @@
       <x:c r="F54" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G54" s="14" t="str"/>
+      <x:c r="G54" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H54" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19849,7 +19937,9 @@
       <x:c r="F55" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G55" s="14" t="str"/>
+      <x:c r="G55" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H55" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19900,7 +19990,9 @@
       <x:c r="F56" s="14" t="str">
         <x:v>embassy, university</x:v>
       </x:c>
-      <x:c r="G56" s="14" t="str"/>
+      <x:c r="G56" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H56" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -19951,7 +20043,9 @@
       <x:c r="F57" s="14" t="str">
         <x:v>other</x:v>
       </x:c>
-      <x:c r="G57" s="14" t="str"/>
+      <x:c r="G57" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H57" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20002,7 +20096,9 @@
       <x:c r="F58" s="14" t="str">
         <x:v>other</x:v>
       </x:c>
-      <x:c r="G58" s="14" t="str"/>
+      <x:c r="G58" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H58" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20106,7 +20202,9 @@
       <x:c r="F60" s="14" t="str">
         <x:v>university, rd, research, general, r_gks</x:v>
       </x:c>
-      <x:c r="G60" s="14" t="str"/>
+      <x:c r="G60" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H60" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20157,7 +20255,9 @@
       <x:c r="F61" s="14" t="str">
         <x:v>embassy, university, global_network</x:v>
       </x:c>
-      <x:c r="G61" s="14" t="str"/>
+      <x:c r="G61" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H61" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20208,7 +20308,9 @@
       <x:c r="F62" s="14" t="str">
         <x:v>embassy, university, general, r_gks</x:v>
       </x:c>
-      <x:c r="G62" s="14" t="str"/>
+      <x:c r="G62" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H62" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20259,7 +20361,9 @@
       <x:c r="F63" s="14" t="str">
         <x:v>university</x:v>
       </x:c>
-      <x:c r="G63" s="14" t="str"/>
+      <x:c r="G63" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H63" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20310,7 +20414,9 @@
       <x:c r="F64" s="14" t="str">
         <x:v>university, global_network</x:v>
       </x:c>
-      <x:c r="G64" s="14" t="str"/>
+      <x:c r="G64" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H64" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20361,7 +20467,9 @@
       <x:c r="F65" s="14" t="str">
         <x:v>other</x:v>
       </x:c>
-      <x:c r="G65" s="14" t="str"/>
+      <x:c r="G65" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H65" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20412,7 +20520,9 @@
       <x:c r="F66" s="14" t="str">
         <x:v>general</x:v>
       </x:c>
-      <x:c r="G66" s="14" t="str"/>
+      <x:c r="G66" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H66" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20781,7 +20891,9 @@
       <x:c r="F73" s="14" t="str">
         <x:v>global_network</x:v>
       </x:c>
-      <x:c r="G73" s="14" t="str"/>
+      <x:c r="G73" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H73" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20832,7 +20944,9 @@
       <x:c r="F74" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G74" s="14" t="str"/>
+      <x:c r="G74" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H74" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20883,7 +20997,9 @@
       <x:c r="F75" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G75" s="14" t="str"/>
+      <x:c r="G75" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H75" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20934,7 +21050,9 @@
       <x:c r="F76" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G76" s="14" t="str"/>
+      <x:c r="G76" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H76" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -20985,7 +21103,9 @@
       <x:c r="F77" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G77" s="14" t="str"/>
+      <x:c r="G77" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H77" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21036,7 +21156,9 @@
       <x:c r="F78" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G78" s="14" t="str"/>
+      <x:c r="G78" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H78" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21087,7 +21209,9 @@
       <x:c r="F79" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G79" s="14" t="str"/>
+      <x:c r="G79" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H79" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21138,7 +21262,9 @@
       <x:c r="F80" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G80" s="14" t="str"/>
+      <x:c r="G80" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H80" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21189,7 +21315,9 @@
       <x:c r="F81" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G81" s="14" t="str"/>
+      <x:c r="G81" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H81" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21240,7 +21368,9 @@
       <x:c r="F82" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G82" s="14" t="str"/>
+      <x:c r="G82" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H82" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21291,7 +21421,9 @@
       <x:c r="F83" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G83" s="14" t="str"/>
+      <x:c r="G83" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H83" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21342,7 +21474,9 @@
       <x:c r="F84" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G84" s="14" t="str"/>
+      <x:c r="G84" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H84" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21393,7 +21527,9 @@
       <x:c r="F85" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G85" s="14" t="str"/>
+      <x:c r="G85" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H85" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21444,7 +21580,9 @@
       <x:c r="F86" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G86" s="14" t="str"/>
+      <x:c r="G86" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H86" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21495,7 +21633,9 @@
       <x:c r="F87" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G87" s="14" t="str"/>
+      <x:c r="G87" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H87" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21546,7 +21686,9 @@
       <x:c r="F88" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G88" s="14" t="str"/>
+      <x:c r="G88" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H88" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21597,7 +21739,9 @@
       <x:c r="F89" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G89" s="14" t="str"/>
+      <x:c r="G89" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H89" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21648,7 +21792,9 @@
       <x:c r="F90" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G90" s="14" t="str"/>
+      <x:c r="G90" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H90" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21699,7 +21845,9 @@
       <x:c r="F91" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G91" s="14" t="str"/>
+      <x:c r="G91" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H91" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21750,7 +21898,9 @@
       <x:c r="F92" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G92" s="14" t="str"/>
+      <x:c r="G92" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H92" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21801,7 +21951,9 @@
       <x:c r="F93" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G93" s="14" t="str"/>
+      <x:c r="G93" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H93" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21852,7 +22004,9 @@
       <x:c r="F94" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G94" s="14" t="str"/>
+      <x:c r="G94" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H94" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21903,7 +22057,9 @@
       <x:c r="F95" s="14" t="str">
         <x:v>global_network</x:v>
       </x:c>
-      <x:c r="G95" s="14" t="str"/>
+      <x:c r="G95" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H95" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -21954,7 +22110,9 @@
       <x:c r="F96" s="14" t="str">
         <x:v>global_network</x:v>
       </x:c>
-      <x:c r="G96" s="14" t="str"/>
+      <x:c r="G96" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H96" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22005,7 +22163,9 @@
       <x:c r="F97" s="14" t="str">
         <x:v>global_network</x:v>
       </x:c>
-      <x:c r="G97" s="14" t="str"/>
+      <x:c r="G97" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H97" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22056,7 +22216,9 @@
       <x:c r="F98" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G98" s="14" t="str"/>
+      <x:c r="G98" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H98" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22107,7 +22269,9 @@
       <x:c r="F99" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G99" s="14" t="str"/>
+      <x:c r="G99" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H99" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22158,7 +22322,9 @@
       <x:c r="F100" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G100" s="14" t="str"/>
+      <x:c r="G100" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H100" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22209,7 +22375,9 @@
       <x:c r="F101" s="14" t="str">
         <x:v>rd</x:v>
       </x:c>
-      <x:c r="G101" s="14" t="str"/>
+      <x:c r="G101" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H101" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22737,7 +22905,9 @@
       <x:c r="F111" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G111" s="14" t="str"/>
+      <x:c r="G111" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H111" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22788,7 +22958,9 @@
       <x:c r="F112" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G112" s="14" t="str"/>
+      <x:c r="G112" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H112" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22839,7 +23011,9 @@
       <x:c r="F113" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G113" s="14" t="str"/>
+      <x:c r="G113" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H113" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22890,7 +23064,9 @@
       <x:c r="F114" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G114" s="14" t="str"/>
+      <x:c r="G114" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H114" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22941,7 +23117,9 @@
       <x:c r="F115" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G115" s="14" t="str"/>
+      <x:c r="G115" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H115" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -22992,7 +23170,9 @@
       <x:c r="F116" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G116" s="14" t="str"/>
+      <x:c r="G116" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H116" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -23043,7 +23223,9 @@
       <x:c r="F117" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G117" s="14" t="str"/>
+      <x:c r="G117" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H117" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -23094,7 +23276,9 @@
       <x:c r="F118" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G118" s="14" t="str"/>
+      <x:c r="G118" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H118" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -23145,7 +23329,9 @@
       <x:c r="F119" s="14" t="str">
         <x:v>university, uic</x:v>
       </x:c>
-      <x:c r="G119" s="14" t="str"/>
+      <x:c r="G119" s="14" t="str">
+        <x:v/>
+      </x:c>
       <x:c r="H119" s="14" t="str">
         <x:v>FALSE</x:v>
       </x:c>
@@ -25844,7 +26030,7 @@
         <x:v>Embassy Track / Type B; University Track UIC separate</x:v>
       </x:c>
       <x:c r="F170" s="14" t="str">
-        <x:v>embassy, university, uic</x:v>
+        <x:v>embassy</x:v>
       </x:c>
       <x:c r="G170" s="14" t="str">
         <x:v>B</x:v>
@@ -25897,7 +26083,7 @@
         <x:v>Embassy Track / Type B; UIC separate</x:v>
       </x:c>
       <x:c r="F171" s="14" t="str">
-        <x:v>embassy, university, uic</x:v>
+        <x:v>embassy</x:v>
       </x:c>
       <x:c r="G171" s="14" t="str">
         <x:v>B</x:v>
@@ -26003,7 +26189,7 @@
         <x:v>Embassy Track / Type B; UIC separate</x:v>
       </x:c>
       <x:c r="F173" s="14" t="str">
-        <x:v>embassy, university, uic</x:v>
+        <x:v>embassy</x:v>
       </x:c>
       <x:c r="G173" s="14" t="str">
         <x:v>B</x:v>
@@ -26056,7 +26242,7 @@
         <x:v>Embassy Track / Type B; UIC English Track separate</x:v>
       </x:c>
       <x:c r="F174" s="14" t="str">
-        <x:v>embassy, university, uic</x:v>
+        <x:v>embassy</x:v>
       </x:c>
       <x:c r="G174" s="14" t="str">
         <x:v>B</x:v>
@@ -26215,7 +26401,7 @@
         <x:v>Embassy Track / Type B / R-GKS; UIC separate</x:v>
       </x:c>
       <x:c r="F177" s="14" t="str">
-        <x:v>embassy, university, uic, r_gks</x:v>
+        <x:v>embassy, r_gks</x:v>
       </x:c>
       <x:c r="G177" s="14" t="str">
         <x:v>B</x:v>
@@ -26533,7 +26719,7 @@
         <x:v>Embassy Track / Type A; UIC separate</x:v>
       </x:c>
       <x:c r="F183" s="14" t="str">
-        <x:v>embassy, university, uic</x:v>
+        <x:v>embassy</x:v>
       </x:c>
       <x:c r="G183" s="14" t="str">
         <x:v>A</x:v>
@@ -26586,7 +26772,7 @@
         <x:v>Embassy Track / Type A; UIC separate</x:v>
       </x:c>
       <x:c r="F184" s="14" t="str">
-        <x:v>embassy, university, uic</x:v>
+        <x:v>embassy</x:v>
       </x:c>
       <x:c r="G184" s="14" t="str">
         <x:v>A</x:v>
@@ -26639,7 +26825,7 @@
         <x:v>Embassy Track / Type A; UIC separate</x:v>
       </x:c>
       <x:c r="F185" s="14" t="str">
-        <x:v>embassy, university, uic</x:v>
+        <x:v>embassy</x:v>
       </x:c>
       <x:c r="G185" s="14" t="str">
         <x:v>A</x:v>
